--- a/analysis/econometrics_outputs/sdid/Graficos/contracts/sdid_levels_cosine_weighted_top_vs_zero.xlsx
+++ b/analysis/econometrics_outputs/sdid/Graficos/contracts/sdid_levels_cosine_weighted_top_vs_zero.xlsx
@@ -507,13 +507,13 @@
         <v>2711.13679245283</v>
       </c>
       <c r="I2" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J2" t="n">
-        <v>-897.297252793878</v>
+        <v>-869.0586264222134</v>
       </c>
       <c r="K2" t="n">
-        <v>243.2805151188929</v>
+        <v>215.0418887472283</v>
       </c>
     </row>
     <row r="3">
@@ -550,13 +550,13 @@
         <v>2419.627358490566</v>
       </c>
       <c r="I3" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J3" t="n">
-        <v>-675.5378188316138</v>
+        <v>-647.2991924599492</v>
       </c>
       <c r="K3" t="n">
-        <v>465.0399490811571</v>
+        <v>436.8013227094925</v>
       </c>
     </row>
     <row r="4">
@@ -593,13 +593,13 @@
         <v>2738.77358490566</v>
       </c>
       <c r="I4" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J4" t="n">
-        <v>-684.0066258918691</v>
+        <v>-655.7679995202045</v>
       </c>
       <c r="K4" t="n">
-        <v>456.5711420209018</v>
+        <v>428.3325156492372</v>
       </c>
     </row>
     <row r="5">
@@ -636,13 +636,13 @@
         <v>2659.037735849056</v>
       </c>
       <c r="I5" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J5" t="n">
-        <v>-641.9965832868786</v>
+        <v>-613.757956915214</v>
       </c>
       <c r="K5" t="n">
-        <v>498.5811846258923</v>
+        <v>470.3425582542277</v>
       </c>
     </row>
     <row r="6">
@@ -679,13 +679,13 @@
         <v>2798.004716981132</v>
       </c>
       <c r="I6" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J6" t="n">
-        <v>-673.9796934512126</v>
+        <v>-645.741067079548</v>
       </c>
       <c r="K6" t="n">
-        <v>466.5980744615583</v>
+        <v>438.3594480898937</v>
       </c>
     </row>
     <row r="7">
@@ -722,13 +722,13 @@
         <v>3268.117924528302</v>
       </c>
       <c r="I7" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J7" t="n">
-        <v>-705.1251590628983</v>
+        <v>-676.8865326912337</v>
       </c>
       <c r="K7" t="n">
-        <v>435.4526088498726</v>
+        <v>407.213982478208</v>
       </c>
     </row>
     <row r="8">
@@ -765,13 +765,13 @@
         <v>3486.396226415094</v>
       </c>
       <c r="I8" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J8" t="n">
-        <v>-987.9195899819481</v>
+        <v>-959.6809636102835</v>
       </c>
       <c r="K8" t="n">
-        <v>152.6581779308228</v>
+        <v>124.4195515591582</v>
       </c>
     </row>
     <row r="9">
@@ -808,13 +808,13 @@
         <v>2852.462264150944</v>
       </c>
       <c r="I9" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J9" t="n">
-        <v>-1040.695305137153</v>
+        <v>-1012.456678765488</v>
       </c>
       <c r="K9" t="n">
-        <v>99.88246277561802</v>
+        <v>71.6438364039534</v>
       </c>
     </row>
     <row r="10">
@@ -851,13 +851,13 @@
         <v>3453.990566037735</v>
       </c>
       <c r="I10" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J10" t="n">
-        <v>-863.2074779916868</v>
+        <v>-834.9688516200222</v>
       </c>
       <c r="K10" t="n">
-        <v>277.3702899210841</v>
+        <v>249.1316635494195</v>
       </c>
     </row>
     <row r="11">
@@ -894,13 +894,13 @@
         <v>3341.033018867925</v>
       </c>
       <c r="I11" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J11" t="n">
-        <v>-774.3628340476823</v>
+        <v>-746.1242076760177</v>
       </c>
       <c r="K11" t="n">
-        <v>366.2149338650886</v>
+        <v>337.976307493424</v>
       </c>
     </row>
     <row r="12">
@@ -937,13 +937,13 @@
         <v>3736</v>
       </c>
       <c r="I12" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J12" t="n">
-        <v>-1025.837879695886</v>
+        <v>-997.5992533242215</v>
       </c>
       <c r="K12" t="n">
-        <v>114.7398882168848</v>
+        <v>86.50126184522014</v>
       </c>
     </row>
     <row r="13">
@@ -980,13 +980,13 @@
         <v>3063.141509433962</v>
       </c>
       <c r="I13" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J13" t="n">
-        <v>-788.2858407427518</v>
+        <v>-760.0472143710872</v>
       </c>
       <c r="K13" t="n">
-        <v>352.2919271700191</v>
+        <v>324.0533007983545</v>
       </c>
     </row>
     <row r="14">
@@ -1023,13 +1023,13 @@
         <v>3085.811320754717</v>
       </c>
       <c r="I14" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J14" t="n">
-        <v>-851.7217810957648</v>
+        <v>-823.4831547241001</v>
       </c>
       <c r="K14" t="n">
-        <v>288.8559868170062</v>
+        <v>260.6173604453415</v>
       </c>
     </row>
     <row r="15">
@@ -1066,13 +1066,13 @@
         <v>2599.768867924528</v>
       </c>
       <c r="I15" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J15" t="n">
-        <v>-414.9293282655765</v>
+        <v>-386.6907018939119</v>
       </c>
       <c r="K15" t="n">
-        <v>725.6484396471944</v>
+        <v>697.4098132755298</v>
       </c>
     </row>
     <row r="16">
@@ -1109,13 +1109,13 @@
         <v>2861.844339622641</v>
       </c>
       <c r="I16" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J16" t="n">
-        <v>-251.6177031894956</v>
+        <v>-223.379076817831</v>
       </c>
       <c r="K16" t="n">
-        <v>888.9600647232753</v>
+        <v>860.7214383516107</v>
       </c>
     </row>
     <row r="17">
@@ -1152,13 +1152,13 @@
         <v>2620.915094339623</v>
       </c>
       <c r="I17" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J17" t="n">
-        <v>-383.5513611322835</v>
+        <v>-355.3127347606189</v>
       </c>
       <c r="K17" t="n">
-        <v>757.0264067804874</v>
+        <v>728.7877804088228</v>
       </c>
     </row>
     <row r="18">
@@ -1195,13 +1195,13 @@
         <v>2855.278301886793</v>
       </c>
       <c r="I18" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J18" t="n">
-        <v>-452.7936009375182</v>
+        <v>-424.5549745658536</v>
       </c>
       <c r="K18" t="n">
-        <v>687.7841669752527</v>
+        <v>659.5455406035881</v>
       </c>
     </row>
     <row r="19">
@@ -1238,13 +1238,13 @@
         <v>3122.665094339623</v>
       </c>
       <c r="I19" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J19" t="n">
-        <v>-451.164264358091</v>
+        <v>-422.9256379864264</v>
       </c>
       <c r="K19" t="n">
-        <v>689.4135035546799</v>
+        <v>661.1748771830153</v>
       </c>
     </row>
     <row r="20">
@@ -1281,13 +1281,13 @@
         <v>3027.099056603774</v>
       </c>
       <c r="I20" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J20" t="n">
-        <v>-500.6627427512738</v>
+        <v>-472.4241163796091</v>
       </c>
       <c r="K20" t="n">
-        <v>639.9150251614972</v>
+        <v>611.6763987898325</v>
       </c>
     </row>
     <row r="21">
@@ -1324,13 +1324,13 @@
         <v>2454.52358490566</v>
       </c>
       <c r="I21" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J21" t="n">
-        <v>-570.2888839563855</v>
+        <v>-542.0502575847208</v>
       </c>
       <c r="K21" t="n">
-        <v>570.2888839563855</v>
+        <v>542.0502575847208</v>
       </c>
     </row>
     <row r="22">
@@ -1367,13 +1367,13 @@
         <v>2818.042452830189</v>
       </c>
       <c r="I22" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J22" t="n">
-        <v>-258.4045260744626</v>
+        <v>-230.165899702798</v>
       </c>
       <c r="K22" t="n">
-        <v>882.1732418383083</v>
+        <v>853.9346154666437</v>
       </c>
     </row>
     <row r="23">
@@ -1410,13 +1410,13 @@
         <v>2618.509433962264</v>
       </c>
       <c r="I23" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J23" t="n">
-        <v>-194.6053781742796</v>
+        <v>-166.366751802615</v>
       </c>
       <c r="K23" t="n">
-        <v>945.9723897384913</v>
+        <v>917.7337633668267</v>
       </c>
     </row>
     <row r="24">
@@ -1453,13 +1453,13 @@
         <v>2523.301886792452</v>
       </c>
       <c r="I24" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J24" t="n">
-        <v>-203.7284761657586</v>
+        <v>-175.489849794094</v>
       </c>
       <c r="K24" t="n">
-        <v>936.8492917470123</v>
+        <v>908.6106653753477</v>
       </c>
     </row>
     <row r="25">
@@ -1496,13 +1496,13 @@
         <v>2064.325471698113</v>
       </c>
       <c r="I25" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J25" t="n">
-        <v>-184.3165772004511</v>
+        <v>-156.0779508287865</v>
       </c>
       <c r="K25" t="n">
-        <v>956.2611907123198</v>
+        <v>928.0225643406552</v>
       </c>
     </row>
     <row r="26">
@@ -1539,13 +1539,13 @@
         <v>2167.622641509434</v>
       </c>
       <c r="I26" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J26" t="n">
-        <v>-260.0572953988694</v>
+        <v>-231.8186690272048</v>
       </c>
       <c r="K26" t="n">
-        <v>880.5204725139015</v>
+        <v>852.2818461422369</v>
       </c>
     </row>
     <row r="27">
@@ -1582,13 +1582,13 @@
         <v>1904.731132075471</v>
       </c>
       <c r="I27" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J27" t="n">
-        <v>-60.64965693264844</v>
+        <v>-32.41103056098382</v>
       </c>
       <c r="K27" t="n">
-        <v>1079.928110980122</v>
+        <v>1051.689484608458</v>
       </c>
     </row>
     <row r="28">
@@ -1625,13 +1625,13 @@
         <v>2338.066037735849</v>
       </c>
       <c r="I28" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J28" t="n">
-        <v>-244.8716593672198</v>
+        <v>-216.6330329955551</v>
       </c>
       <c r="K28" t="n">
-        <v>895.7061085455512</v>
+        <v>867.4674821738865</v>
       </c>
     </row>
     <row r="29">
@@ -1668,13 +1668,13 @@
         <v>1989.075471698113</v>
       </c>
       <c r="I29" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J29" t="n">
-        <v>-159.655286877871</v>
+        <v>-131.4166605062064</v>
       </c>
       <c r="K29" t="n">
-        <v>980.9224810348999</v>
+        <v>952.6838546632353</v>
       </c>
     </row>
     <row r="30">
@@ -1711,13 +1711,13 @@
         <v>2376.551886792452</v>
       </c>
       <c r="I30" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J30" t="n">
-        <v>-263.8252503593071</v>
+        <v>-235.5866239876425</v>
       </c>
       <c r="K30" t="n">
-        <v>876.7525175534638</v>
+        <v>848.5138911817992</v>
       </c>
     </row>
     <row r="31">
@@ -1754,13 +1754,13 @@
         <v>2582.896226415094</v>
       </c>
       <c r="I31" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J31" t="n">
-        <v>-210.8631383690456</v>
+        <v>-182.624511997381</v>
       </c>
       <c r="K31" t="n">
-        <v>929.7146295437253</v>
+        <v>901.4760031720607</v>
       </c>
     </row>
     <row r="32">
@@ -1797,13 +1797,13 @@
         <v>2554.811320754717</v>
       </c>
       <c r="I32" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J32" t="n">
-        <v>-286.3992004506035</v>
+        <v>-258.1605740789389</v>
       </c>
       <c r="K32" t="n">
-        <v>854.1785674621674</v>
+        <v>825.9399410905028</v>
       </c>
     </row>
     <row r="33">
@@ -1840,13 +1840,13 @@
         <v>2080.533018867924</v>
       </c>
       <c r="I33" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J33" t="n">
-        <v>-458.3547695315528</v>
+        <v>-430.1161431598882</v>
       </c>
       <c r="K33" t="n">
-        <v>682.2229983812181</v>
+        <v>653.9843720095535</v>
       </c>
     </row>
     <row r="34">
@@ -1883,13 +1883,13 @@
         <v>2389.122641509433</v>
       </c>
       <c r="I34" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J34" t="n">
-        <v>-209.7831018504814</v>
+        <v>-181.5444754788168</v>
       </c>
       <c r="K34" t="n">
-        <v>930.7946660622895</v>
+        <v>902.5560396906249</v>
       </c>
     </row>
     <row r="35">
@@ -1926,13 +1926,13 @@
         <v>2399.528301886792</v>
       </c>
       <c r="I35" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J35" t="n">
-        <v>-143.5355364213888</v>
+        <v>-115.2969100497241</v>
       </c>
       <c r="K35" t="n">
-        <v>997.0422314913822</v>
+        <v>968.8036051197175</v>
       </c>
     </row>
     <row r="36">
@@ -1969,13 +1969,13 @@
         <v>2316.693396226415</v>
       </c>
       <c r="I36" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J36" t="n">
-        <v>-4.313533986818129</v>
+        <v>23.92509238484649</v>
       </c>
       <c r="K36" t="n">
-        <v>1136.264233925953</v>
+        <v>1108.025607554288</v>
       </c>
     </row>
     <row r="37">
@@ -2012,13 +2012,13 @@
         <v>1928.165094339622</v>
       </c>
       <c r="I37" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J37" t="n">
-        <v>-161.7529740355092</v>
+        <v>-133.5143476638445</v>
       </c>
       <c r="K37" t="n">
-        <v>978.8247938772618</v>
+        <v>950.5861675055971</v>
       </c>
     </row>
     <row r="38">
@@ -2055,13 +2055,13 @@
         <v>2210.429245283019</v>
       </c>
       <c r="I38" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J38" t="n">
-        <v>-287.5171249789055</v>
+        <v>-259.2784986072409</v>
       </c>
       <c r="K38" t="n">
-        <v>853.0606429338654</v>
+        <v>824.8220165622008</v>
       </c>
     </row>
     <row r="39">
@@ -2098,13 +2098,13 @@
         <v>2021.037735849056</v>
       </c>
       <c r="I39" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J39" t="n">
-        <v>-132.4723897384915</v>
+        <v>-104.2337633668269</v>
       </c>
       <c r="K39" t="n">
-        <v>1008.105378174279</v>
+        <v>979.8667518026148</v>
       </c>
     </row>
     <row r="40">
@@ -2141,13 +2141,13 @@
         <v>1954.193396226415</v>
       </c>
       <c r="I40" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J40" t="n">
-        <v>-80.89417914810838</v>
+        <v>-52.65555277644376</v>
       </c>
       <c r="K40" t="n">
-        <v>1059.683588764663</v>
+        <v>1031.444962392998</v>
       </c>
     </row>
     <row r="41">
@@ -2184,13 +2184,13 @@
         <v>2184.867924528302</v>
       </c>
       <c r="I41" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J41" t="n">
-        <v>-165.286449385479</v>
+        <v>-137.0478230138144</v>
       </c>
       <c r="K41" t="n">
-        <v>975.2913185272919</v>
+        <v>947.0526921556273</v>
       </c>
     </row>
     <row r="42">
@@ -2227,13 +2227,13 @@
         <v>2269.801886792453</v>
       </c>
       <c r="I42" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J42" t="n">
-        <v>-224.1317019722107</v>
+        <v>-195.8930756005461</v>
       </c>
       <c r="K42" t="n">
-        <v>916.4460659405602</v>
+        <v>888.2074395688956</v>
       </c>
     </row>
     <row r="43">
@@ -2270,13 +2270,13 @@
         <v>2416.264150943396</v>
       </c>
       <c r="I43" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J43" t="n">
-        <v>-150.1423532199281</v>
+        <v>-121.9037268482634</v>
       </c>
       <c r="K43" t="n">
-        <v>990.4354146928429</v>
+        <v>962.1967883211782</v>
       </c>
     </row>
     <row r="44">
@@ -2313,13 +2313,13 @@
         <v>2747.603773584905</v>
       </c>
       <c r="I44" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J44" t="n">
-        <v>-335.2964919904691</v>
+        <v>-307.0578656188045</v>
       </c>
       <c r="K44" t="n">
-        <v>805.2812759223018</v>
+        <v>777.0426495506372</v>
       </c>
     </row>
     <row r="45">
@@ -2356,13 +2356,13 @@
         <v>1981.77358490566</v>
       </c>
       <c r="I45" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J45" t="n">
-        <v>-380.7082387950954</v>
+        <v>-352.4696124234308</v>
       </c>
       <c r="K45" t="n">
-        <v>759.8695291176755</v>
+        <v>731.6309027460109</v>
       </c>
     </row>
     <row r="46">
@@ -2399,13 +2399,13 @@
         <v>2438.816037735849</v>
       </c>
       <c r="I46" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J46" t="n">
-        <v>-210.8635948510903</v>
+        <v>-182.6249684794257</v>
       </c>
       <c r="K46" t="n">
-        <v>929.7141730616806</v>
+        <v>901.475546690016</v>
       </c>
     </row>
     <row r="47">
@@ -2442,13 +2442,13 @@
         <v>2665.009433962264</v>
       </c>
       <c r="I47" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J47" t="n">
-        <v>-299.395700754925</v>
+        <v>-271.1570743832604</v>
       </c>
       <c r="K47" t="n">
-        <v>841.1820671578459</v>
+        <v>812.9434407861813</v>
       </c>
     </row>
     <row r="48">
@@ -2485,13 +2485,13 @@
         <v>2297.207547169811</v>
       </c>
       <c r="I48" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J48" t="n">
-        <v>-229.1986526721496</v>
+        <v>-200.960026300485</v>
       </c>
       <c r="K48" t="n">
-        <v>911.3791152406213</v>
+        <v>883.1404888689567</v>
       </c>
     </row>
     <row r="49">
@@ -2528,13 +2528,13 @@
         <v>2030.721698113208</v>
       </c>
       <c r="I49" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J49" t="n">
-        <v>-189.0757068413527</v>
+        <v>-160.8370804696881</v>
       </c>
       <c r="K49" t="n">
-        <v>951.5020610714182</v>
+        <v>923.2634346997536</v>
       </c>
     </row>
     <row r="50">
@@ -2571,13 +2571,13 @@
         <v>2226.193396226415</v>
       </c>
       <c r="I50" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J50" t="n">
-        <v>-312.2570823739145</v>
+        <v>-284.0184560022499</v>
       </c>
       <c r="K50" t="n">
-        <v>828.3206855388564</v>
+        <v>800.0820591671918</v>
       </c>
     </row>
     <row r="51">
@@ -2614,13 +2614,13 @@
         <v>1966.688679245283</v>
       </c>
       <c r="I51" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J51" t="n">
-        <v>-156.2201073282665</v>
+        <v>-127.9814809566019</v>
       </c>
       <c r="K51" t="n">
-        <v>984.3576605845044</v>
+        <v>956.1190342128398</v>
       </c>
     </row>
     <row r="52">
@@ -2657,13 +2657,13 @@
         <v>2116.632075471698</v>
       </c>
       <c r="I52" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J52" t="n">
-        <v>-169.9135035546817</v>
+        <v>-141.6748771830171</v>
       </c>
       <c r="K52" t="n">
-        <v>970.6642643580892</v>
+        <v>942.4256379864246</v>
       </c>
     </row>
     <row r="53">
@@ -2700,13 +2700,13 @@
         <v>2003.52358490566</v>
       </c>
       <c r="I53" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J53" t="n">
-        <v>-147.9017871821923</v>
+        <v>-119.6631608105276</v>
       </c>
       <c r="K53" t="n">
-        <v>992.6759807305787</v>
+        <v>964.437354358914</v>
       </c>
     </row>
     <row r="54">
@@ -2743,13 +2743,13 @@
         <v>2309.650943396226</v>
       </c>
       <c r="I54" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J54" t="n">
-        <v>-278.7226940598553</v>
+        <v>-250.4840676881906</v>
       </c>
       <c r="K54" t="n">
-        <v>861.8550738529157</v>
+        <v>833.616447481251</v>
       </c>
     </row>
     <row r="55">
@@ -2786,13 +2786,13 @@
         <v>2640.556603773585</v>
       </c>
       <c r="I55" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J55" t="n">
-        <v>-265.5719028243109</v>
+        <v>-237.3332764526463</v>
       </c>
       <c r="K55" t="n">
-        <v>875.00586508846</v>
+        <v>846.7672387167954</v>
       </c>
     </row>
     <row r="56">
@@ -2829,13 +2829,13 @@
         <v>3000.971698113208</v>
       </c>
       <c r="I56" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J56" t="n">
-        <v>-562.9628036155461</v>
+        <v>-534.7241772438815</v>
       </c>
       <c r="K56" t="n">
-        <v>577.6149642972248</v>
+        <v>549.3763379255602</v>
       </c>
     </row>
     <row r="57">
@@ -2872,13 +2872,13 @@
         <v>2042.193396226415</v>
       </c>
       <c r="I57" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J57" t="n">
-        <v>-450.2006307610113</v>
+        <v>-421.9620043893467</v>
       </c>
       <c r="K57" t="n">
-        <v>690.3771371517596</v>
+        <v>662.138510780095</v>
       </c>
     </row>
     <row r="58">
@@ -2915,13 +2915,13 @@
         <v>2691.632075471698</v>
       </c>
       <c r="I58" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J58" t="n">
-        <v>-301.4215680708105</v>
+        <v>-273.1829416991459</v>
       </c>
       <c r="K58" t="n">
-        <v>839.1561998419604</v>
+        <v>810.9175734702958</v>
       </c>
     </row>
     <row r="59">
@@ -2958,13 +2958,13 @@
         <v>2644.966981132075</v>
       </c>
       <c r="I59" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J59" t="n">
-        <v>-293.6355059892528</v>
+        <v>-265.3968796175882</v>
       </c>
       <c r="K59" t="n">
-        <v>846.9422619235181</v>
+        <v>818.7036355518535</v>
       </c>
     </row>
     <row r="60">
@@ -3001,13 +3001,13 @@
         <v>2367.330188679245</v>
       </c>
       <c r="I60" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J60" t="n">
-        <v>-294.8858103106159</v>
+        <v>-266.6471839389512</v>
       </c>
       <c r="K60" t="n">
-        <v>845.6919576021551</v>
+        <v>817.4533312304904</v>
       </c>
     </row>
     <row r="61">
@@ -3044,13 +3044,13 @@
         <v>2200.457547169811</v>
       </c>
       <c r="I61" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J61" t="n">
-        <v>-301.2873623495691</v>
+        <v>-273.0487359779045</v>
       </c>
       <c r="K61" t="n">
-        <v>839.2904055632018</v>
+        <v>811.0517791915372</v>
       </c>
     </row>
     <row r="62">
@@ -3087,13 +3087,13 @@
         <v>2249.122641509434</v>
       </c>
       <c r="I62" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J62" t="n">
-        <v>-434.3879405601599</v>
+        <v>-406.1493141884953</v>
       </c>
       <c r="K62" t="n">
-        <v>706.189827352611</v>
+        <v>677.9512009809464</v>
       </c>
     </row>
     <row r="63">
@@ -3130,13 +3130,13 @@
         <v>2071.358490566038</v>
       </c>
       <c r="I63" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J63" t="n">
-        <v>-269.1479831651509</v>
+        <v>-240.9093567934863</v>
       </c>
       <c r="K63" t="n">
-        <v>871.42978474762</v>
+        <v>843.1911583759554</v>
       </c>
     </row>
     <row r="64">
@@ -3173,13 +3173,13 @@
         <v>2364.75</v>
       </c>
       <c r="I64" t="n">
-        <v>290.9637163042783</v>
+        <v>276.5562538697556</v>
       </c>
       <c r="J64" t="n">
-        <v>-324.3701377604029</v>
+        <v>-296.1315113887383</v>
       </c>
       <c r="K64" t="n">
-        <v>816.207630152368</v>
+        <v>787.9690037807034</v>
       </c>
     </row>
   </sheetData>
